--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\teste_PHYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\teste_PHYTHON\PREP_ELEIÇÕES 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{558DCC2D-7873-4048-A29C-A0025B46F5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E0EDE7-8742-4184-A44F-19B7B972718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1800" windowWidth="13245" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONVOCATÓRIA" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
     <t>Mário Brito Fonseca</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento </t>
+    <t>numero_documento</t>
   </si>
 </sst>
 </file>
@@ -1079,1429 +1079,1432 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="C3" s="4">
-        <v>123456</v>
+        <v>123566</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="C4" s="4">
-        <v>123457</v>
+        <v>123590</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
+      <c r="B5" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="C5" s="4">
-        <v>123458</v>
+        <v>123614</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4">
-        <v>123459</v>
+        <v>123508</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
+      <c r="B7" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="C7" s="4">
-        <v>123460</v>
+        <v>123545</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
+      <c r="B8" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="C8" s="4">
-        <v>123461</v>
+        <v>123586</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="C9" s="4">
-        <v>123462</v>
+        <v>123521</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4">
-        <v>123463</v>
+        <v>123491</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4">
-        <v>123464</v>
+        <v>123520</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4">
-        <v>123465</v>
+        <v>123523</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>10</v>
+      <c r="B13" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="C13" s="4">
-        <v>123466</v>
+        <v>123626</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>11</v>
+        <v>175</v>
       </c>
       <c r="C14" s="4">
-        <v>123467</v>
+        <v>123630</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4">
-        <v>123468</v>
+        <v>123497</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4">
-        <v>123469</v>
+        <v>123473</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="C17" s="4">
-        <v>123470</v>
+        <v>123562</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C18" s="4">
-        <v>123471</v>
+        <v>123462</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="C19" s="4">
-        <v>123472</v>
+        <v>123574</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="C20" s="4">
-        <v>123473</v>
+        <v>123573</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C21" s="4">
-        <v>123474</v>
+        <v>123531</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C22" s="4">
-        <v>123475</v>
+        <v>123517</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4">
-        <v>123476</v>
+        <v>123514</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C24" s="4">
-        <v>123477</v>
+        <v>123503</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="C25" s="4">
-        <v>123478</v>
+        <v>123529</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26" s="4">
-        <v>123479</v>
+        <v>123474</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C27" s="4">
-        <v>123480</v>
+        <v>123530</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>25</v>
+      <c r="B28" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="C28" s="4">
-        <v>123481</v>
+        <v>123578</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>26</v>
+      <c r="B29" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C29" s="4">
-        <v>123482</v>
+        <v>123541</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C30" s="4">
-        <v>123483</v>
+        <v>123555</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="C31" s="4">
-        <v>123484</v>
+        <v>123542</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="C32" s="4">
-        <v>123485</v>
+        <v>123625</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>30</v>
+      <c r="B33" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="C33" s="4">
-        <v>123486</v>
+        <v>123604</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C34" s="4">
-        <v>123487</v>
+        <v>123535</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="C35" s="4">
-        <v>123488</v>
+        <v>123596</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C36" s="4">
-        <v>123489</v>
+        <v>123525</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
-        <v>34</v>
+      <c r="B37" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C37" s="4">
-        <v>123490</v>
+        <v>123496</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C38" s="4">
-        <v>123491</v>
+        <v>123554</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C39" s="4">
-        <v>123492</v>
+        <v>123505</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C40" s="4">
-        <v>123493</v>
+        <v>123470</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4">
-        <v>123494</v>
+        <v>123460</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
-        <v>39</v>
+      <c r="B42" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C42" s="4">
-        <v>123495</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
-        <v>40</v>
+      <c r="B43" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C43" s="4">
-        <v>123496</v>
+        <v>123538</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="3" t="s">
-        <v>41</v>
+      <c r="B44" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C44" s="4">
-        <v>123497</v>
+        <v>123537</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="3" t="s">
-        <v>42</v>
+      <c r="B45" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C45" s="4">
-        <v>123498</v>
+        <v>123484</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4">
-        <v>123499</v>
+        <v>123501</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="C47" s="4">
-        <v>123500</v>
+        <v>123461</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C48" s="4">
-        <v>123501</v>
+        <v>123631</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="C49" s="4">
-        <v>123502</v>
+        <v>123551</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C50" s="4">
-        <v>123503</v>
+        <v>123483</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
-        <v>48</v>
+      <c r="B51" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C51" s="4">
-        <v>123504</v>
+        <v>123580</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="C52" s="4">
-        <v>123505</v>
+        <v>123582</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C53" s="4">
-        <v>123506</v>
+        <v>123507</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
-        <v>51</v>
+      <c r="B54" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C54" s="4">
-        <v>123507</v>
+        <v>123536</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="C55" s="4">
-        <v>123508</v>
+        <v>123597</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C56" s="4">
-        <v>123509</v>
+        <v>123526</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="C57" s="4">
-        <v>123510</v>
+        <v>123581</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C58" s="4">
-        <v>123511</v>
+        <v>123527</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="C59" s="4">
-        <v>123512</v>
+        <v>123570</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="C60" s="4">
-        <v>123513</v>
+        <v>123599</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="3" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C61" s="4">
-        <v>123514</v>
+        <v>123550</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
-        <v>59</v>
+      <c r="B62" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C62" s="4">
-        <v>123515</v>
+        <v>123547</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="C63" s="4">
-        <v>123516</v>
+        <v>123594</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C64" s="4">
-        <v>123517</v>
+        <v>123557</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="C65" s="4">
-        <v>123518</v>
+        <v>123601</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4">
-        <v>123519</v>
+        <v>123456</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C67" s="4">
-        <v>123520</v>
+        <v>123532</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="3" t="s">
-        <v>65</v>
+      <c r="B68" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C68" s="4">
-        <v>123521</v>
+        <v>123624</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="3" t="s">
-        <v>66</v>
+      <c r="B69" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="C69" s="4">
-        <v>123522</v>
+        <v>123485</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C70" s="4">
-        <v>123523</v>
+        <v>123548</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="3" t="s">
-        <v>68</v>
+      <c r="B71" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="C71" s="4">
-        <v>123524</v>
+        <v>123611</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="C72" s="4">
-        <v>123525</v>
+        <v>123492</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C73" s="4">
-        <v>123526</v>
+        <v>123572</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>71</v>
+      <c r="B74" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C74" s="4">
-        <v>123527</v>
+        <v>123544</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C75" s="4">
-        <v>123528</v>
+        <v>123469</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C76" s="4">
-        <v>123529</v>
+        <v>123498</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C77" s="4">
-        <v>123530</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C78" s="4">
-        <v>123531</v>
+        <v>123564</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="C79" s="4">
-        <v>123532</v>
+        <v>123489</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="7" t="s">
-        <v>77</v>
+      <c r="B80" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C80" s="4">
-        <v>123533</v>
+        <v>123475</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="3" t="s">
-        <v>78</v>
+      <c r="B81" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="C81" s="4">
-        <v>123534</v>
+        <v>123610</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="5" t="s">
-        <v>80</v>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C82" s="4">
-        <v>123535</v>
+        <v>123471</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="5" t="s">
-        <v>81</v>
+      <c r="B83" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="C83" s="4">
-        <v>123536</v>
+        <v>123571</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="5" t="s">
-        <v>82</v>
+      <c r="B84" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="C84" s="4">
-        <v>123537</v>
+        <v>123588</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="5" t="s">
-        <v>83</v>
+      <c r="B85" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C85" s="4">
-        <v>123538</v>
+        <v>123458</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="5" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="C86" s="4">
-        <v>123539</v>
+        <v>123486</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="5" t="s">
-        <v>85</v>
+      <c r="B87" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C87" s="4">
-        <v>123540</v>
+        <v>123494</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="5" t="s">
-        <v>86</v>
+      <c r="B88" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C88" s="4">
-        <v>123541</v>
+        <v>123561</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="5" t="s">
-        <v>87</v>
+      <c r="B89" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C89" s="4">
-        <v>123542</v>
+        <v>123488</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="5" t="s">
-        <v>88</v>
+      <c r="B90" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C90" s="4">
-        <v>123543</v>
+        <v>123560</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="5" t="s">
-        <v>89</v>
+      <c r="B91" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="C91" s="4">
-        <v>123544</v>
+        <v>123513</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="5" t="s">
-        <v>90</v>
+      <c r="B92" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C92" s="4">
-        <v>123545</v>
+        <v>123479</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="5" t="s">
-        <v>91</v>
+      <c r="B93" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="C93" s="4">
-        <v>123546</v>
+        <v>123619</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="5" t="s">
-        <v>92</v>
+      <c r="B94" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="C94" s="4">
-        <v>123547</v>
+        <v>123585</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C95" s="4">
-        <v>123548</v>
+        <v>123556</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="3" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C96" s="4">
-        <v>123549</v>
+        <v>123481</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="3" t="s">
-        <v>95</v>
+      <c r="B97" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C97" s="4">
-        <v>123550</v>
+        <v>123540</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="C98" s="4">
-        <v>123551</v>
+        <v>123608</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="3" t="s">
-        <v>97</v>
+      <c r="B99" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="C99" s="4">
-        <v>123552</v>
+        <v>123613</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="3" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C100" s="4">
-        <v>123553</v>
+        <v>123534</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="3" t="s">
-        <v>99</v>
+      <c r="B101" s="8" t="s">
+        <v>163</v>
       </c>
       <c r="C101" s="4">
-        <v>123554</v>
+        <v>123618</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="3" t="s">
-        <v>100</v>
+      <c r="B102" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C102" s="4">
-        <v>123555</v>
+        <v>123627</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C103" s="4">
-        <v>123556</v>
+        <v>123565</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="3" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="C104" s="4">
-        <v>123557</v>
+        <v>123493</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="3" t="s">
-        <v>103</v>
+      <c r="B105" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="C105" s="4">
-        <v>123558</v>
+        <v>123622</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="3" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="C106" s="4">
-        <v>123559</v>
+        <v>123467</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C107" s="4">
-        <v>123560</v>
+        <v>123568</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="3" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="C108" s="4">
-        <v>123561</v>
+        <v>123490</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="3" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C109" s="4">
-        <v>123562</v>
+        <v>123589</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="3" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C110" s="4">
-        <v>123563</v>
+        <v>123524</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="3" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="C111" s="4">
-        <v>123564</v>
+        <v>123472</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="3" t="s">
-        <v>110</v>
+      <c r="B112" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C112" s="4">
-        <v>123565</v>
+        <v>123533</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="3" t="s">
-        <v>111</v>
+      <c r="B113" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C113" s="4">
-        <v>123566</v>
+        <v>123495</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="3" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="C114" s="4">
-        <v>123567</v>
+        <v>123511</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="3" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="C115" s="4">
-        <v>123568</v>
+        <v>123602</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="3" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="C116" s="4">
-        <v>123569</v>
+        <v>123465</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="3" t="s">
-        <v>115</v>
+      <c r="B117" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C117" s="4">
-        <v>123570</v>
+        <v>123487</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="3" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C118" s="4">
-        <v>123571</v>
+        <v>123516</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B119" s="3" t="s">
-        <v>117</v>
+      <c r="B119" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C119" s="4">
-        <v>123572</v>
+        <v>123543</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="3" t="s">
-        <v>118</v>
+      <c r="B120" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="C120" s="4">
-        <v>123573</v>
+        <v>123620</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="3" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="C121" s="4">
-        <v>123574</v>
+        <v>123518</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="3" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="C122" s="4">
-        <v>123575</v>
+        <v>123509</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C123" s="4">
-        <v>123576</v>
+        <v>123552</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="8" t="s">
-        <v>122</v>
+      <c r="B124" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="C124" s="4">
-        <v>123577</v>
+        <v>123592</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="6" t="s">
-        <v>123</v>
+      <c r="B125" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="C125" s="4">
-        <v>123578</v>
+        <v>123600</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="6" t="s">
-        <v>124</v>
+      <c r="B126" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C126" s="4">
-        <v>123579</v>
+        <v>123504</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="5" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="C127" s="4">
-        <v>123580</v>
+        <v>123539</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="3" t="s">
-        <v>126</v>
+      <c r="B128" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="C128" s="4">
-        <v>123581</v>
+        <v>123579</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="3" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C129" s="4">
-        <v>123582</v>
+        <v>123558</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="3" t="s">
-        <v>128</v>
+      <c r="B130" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="C130" s="4">
-        <v>123583</v>
+        <v>123617</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="3" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C131" s="4">
-        <v>123584</v>
+        <v>123609</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="6" t="s">
-        <v>130</v>
+      <c r="B132" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C132" s="4">
-        <v>123585</v>
+        <v>123466</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="C133" s="4">
-        <v>123586</v>
+        <v>123615</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="3" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C134" s="4">
-        <v>123587</v>
+        <v>123603</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="3" t="s">
-        <v>133</v>
+      <c r="B135" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="C135" s="4">
-        <v>123588</v>
+        <v>123616</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B136" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C136" s="4">
-        <v>123589</v>
+        <v>123576</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B137" s="3" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C137" s="4">
-        <v>123590</v>
+        <v>123632</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B138" s="3" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="C138" s="4">
-        <v>123591</v>
+        <v>123633</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B139" s="3" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="C139" s="4">
-        <v>123592</v>
+        <v>123468</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B140" s="3" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="C140" s="4">
-        <v>123593</v>
+        <v>123629</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B141" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C141" s="4">
-        <v>123594</v>
+        <v>123587</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B142" s="3" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="C142" s="4">
-        <v>123595</v>
+        <v>123549</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="3" t="s">
-        <v>141</v>
+      <c r="B143" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="C143" s="4">
-        <v>123596</v>
+        <v>123577</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B144" s="3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="C144" s="4">
-        <v>123597</v>
+        <v>123506</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C145" s="4">
-        <v>123598</v>
+        <v>123591</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="3" t="s">
-        <v>144</v>
+      <c r="B146" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C146" s="4">
-        <v>123599</v>
+        <v>123546</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C147" s="4">
-        <v>123600</v>
+        <v>123598</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C148" s="4">
-        <v>123601</v>
+        <v>123607</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="3" t="s">
-        <v>147</v>
+      <c r="B149" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="C149" s="4">
-        <v>123602</v>
+        <v>123621</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="3" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="C150" s="4">
-        <v>123603</v>
+        <v>123502</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C151" s="4">
-        <v>123604</v>
+        <v>123593</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B152" s="3" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C152" s="4">
-        <v>123605</v>
+        <v>123522</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="3" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="C153" s="4">
-        <v>123606</v>
+        <v>123499</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="3" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C154" s="4">
-        <v>123607</v>
+        <v>123563</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B155" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="C155" s="4">
-        <v>123608</v>
+        <v>123569</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B156" s="3" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C156" s="4">
-        <v>123609</v>
+        <v>123482</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B157" s="6" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C157" s="4">
-        <v>123610</v>
+        <v>123623</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="6" t="s">
-        <v>156</v>
+      <c r="B158" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C158" s="4">
-        <v>123611</v>
+        <v>123480</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C159" s="4">
+        <v>123512</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B160" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C160" s="4">
+        <v>123595</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="4">
+        <v>123463</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" s="4">
+        <v>123476</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B163" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C163" s="4">
+        <v>123477</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B164" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C164" s="4">
+        <v>123457</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="4">
+        <v>123459</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B166" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C166" s="4">
+        <v>123583</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C167" s="4">
+        <v>123575</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B168" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C168" s="4">
+        <v>123515</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B169" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C169" s="4">
+        <v>123606</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B170" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C170" s="4">
+        <v>123553</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B171" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C171" s="4">
+        <v>123478</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B172" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C172" s="4">
+        <v>123519</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B173" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C173" s="4">
+        <v>123528</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" s="4">
+        <v>123464</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B175" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C175" s="4">
+        <v>123559</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B176" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C176" s="4">
         <v>123612</v>
-      </c>
-    </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C160" s="4">
-        <v>123613</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C161" s="4">
-        <v>123614</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C162" s="4">
-        <v>123615</v>
-      </c>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C163" s="4">
-        <v>123616</v>
-      </c>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C164" s="4">
-        <v>123617</v>
-      </c>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C165" s="4">
-        <v>123618</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C166" s="4">
-        <v>123619</v>
-      </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C167" s="4">
-        <v>123620</v>
-      </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C168" s="4">
-        <v>123621</v>
-      </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C169" s="4">
-        <v>123622</v>
-      </c>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B170" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C170" s="4">
-        <v>123623</v>
-      </c>
-    </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B171" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C171" s="4">
-        <v>123624</v>
-      </c>
-    </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B172" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C172" s="4">
-        <v>123625</v>
-      </c>
-    </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B173" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C173" s="4">
-        <v>123626</v>
-      </c>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B174" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C174" s="4">
-        <v>123627</v>
-      </c>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B175" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C175" s="4">
-        <v>123628</v>
-      </c>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B176" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C176" s="4">
-        <v>123629</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="3" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C177" s="4">
-        <v>123630</v>
+        <v>123605</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="3" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="C178" s="4">
-        <v>123631</v>
+        <v>123510</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B179" s="3" t="s">
-        <v>176</v>
+      <c r="B179" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="C179" s="4">
-        <v>123632</v>
+        <v>123628</v>
       </c>
     </row>
     <row r="180" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B180" s="9" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="C180" s="4">
-        <v>123633</v>
+        <v>123584</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C180">
+    <sortCondition ref="B1:B180"/>
+  </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\teste_PHYTHON\PREP_ELEIÇÕES 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E0EDE7-8742-4184-A44F-19B7B972718B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9801CD3-3C46-471E-A016-60DB83E6BBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1800" windowWidth="13245" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -675,7 +675,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -688,21 +688,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -767,16 +752,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1060,7 +1043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C180"/>
+  <dimension ref="B1:C179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
@@ -1068,1442 +1051,1441 @@
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>178</v>
+      <c r="B2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="3">
+        <v>123566</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="4">
-        <v>123566</v>
+      <c r="B3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="3">
+        <v>123590</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="4">
-        <v>123590</v>
+      <c r="B4" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="3">
+        <v>123614</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="4">
-        <v>123614</v>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3">
+        <v>123508</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4">
-        <v>123508</v>
+      <c r="B6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="3">
+        <v>123545</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="4">
-        <v>123545</v>
+        <v>131</v>
+      </c>
+      <c r="C7" s="3">
+        <v>123586</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="4">
-        <v>123586</v>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3">
+        <v>123521</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="4">
-        <v>123521</v>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3">
+        <v>123491</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="4">
-        <v>123491</v>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3">
+        <v>123520</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="4">
-        <v>123520</v>
+      <c r="B11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="3">
+        <v>123523</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="4">
-        <v>123523</v>
+      <c r="B12" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="3">
+        <v>123626</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="4">
-        <v>123626</v>
+      <c r="B13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="3">
+        <v>123630</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="4">
-        <v>123630</v>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3">
+        <v>123497</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="4">
-        <v>123497</v>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3">
+        <v>123473</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="4">
-        <v>123473</v>
+      <c r="B16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="3">
+        <v>123562</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="4">
-        <v>123562</v>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>123462</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="4">
-        <v>123462</v>
+      <c r="B18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="3">
+        <v>123574</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="4">
-        <v>123574</v>
+      <c r="B19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="3">
+        <v>123573</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="4">
-        <v>123573</v>
+      <c r="B20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="3">
+        <v>123531</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="4">
-        <v>123531</v>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3">
+        <v>123517</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="4">
-        <v>123517</v>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="3">
+        <v>123514</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="4">
-        <v>123514</v>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3">
+        <v>123503</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="4">
-        <v>123503</v>
+      <c r="B24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="3">
+        <v>123529</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="4">
-        <v>123529</v>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3">
+        <v>123474</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="4">
-        <v>123474</v>
+      <c r="B26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="3">
+        <v>123530</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="4">
-        <v>123530</v>
+      <c r="B27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="3">
+        <v>123578</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="4">
-        <v>123578</v>
+      <c r="B28" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="3">
+        <v>123541</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="4">
-        <v>123541</v>
+      <c r="B29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="3">
+        <v>123555</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="4">
-        <v>123555</v>
+      <c r="B30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="3">
+        <v>123542</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="4">
-        <v>123542</v>
+        <v>170</v>
+      </c>
+      <c r="C31" s="3">
+        <v>123625</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" s="4">
-        <v>123625</v>
+      <c r="B32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="3">
+        <v>123604</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="4">
-        <v>123604</v>
+      <c r="B33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="3">
+        <v>123535</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="4">
-        <v>123535</v>
+      <c r="B34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="3">
+        <v>123596</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" s="4">
-        <v>123596</v>
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3">
+        <v>123525</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="4">
-        <v>123525</v>
+      <c r="B36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="3">
+        <v>123496</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="4">
-        <v>123496</v>
+      <c r="B37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="3">
+        <v>123554</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="4">
-        <v>123554</v>
+      <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="3">
+        <v>123505</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="4">
-        <v>123505</v>
+      <c r="B39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="3">
+        <v>123470</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="4">
-        <v>123470</v>
+      <c r="B40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="3">
+        <v>123460</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" s="4">
-        <v>123460</v>
+      <c r="B41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="3">
+        <v>123500</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="4">
-        <v>123500</v>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="3">
+        <v>123538</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="4">
-        <v>123538</v>
+      <c r="B43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="3">
+        <v>123537</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="4">
-        <v>123537</v>
+      <c r="B44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="3">
+        <v>123484</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="4">
-        <v>123484</v>
+      <c r="B45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="3">
+        <v>123501</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" s="4">
-        <v>123501</v>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="3">
+        <v>123461</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="4">
-        <v>123461</v>
+      <c r="C47" s="3">
+        <v>123631</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="4">
-        <v>123631</v>
+      <c r="B48" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="3">
+        <v>123551</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="4">
-        <v>123551</v>
+      <c r="B49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="3">
+        <v>123483</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="4">
-        <v>123483</v>
+      <c r="B50" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="3">
+        <v>123580</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C51" s="4">
-        <v>123580</v>
+      <c r="B51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="3">
+        <v>123582</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="4">
-        <v>123582</v>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3">
+        <v>123507</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="4">
-        <v>123507</v>
+      <c r="B53" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="3">
+        <v>123536</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="4">
-        <v>123536</v>
+      <c r="B54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="3">
+        <v>123597</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="4">
-        <v>123597</v>
+      <c r="B55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="3">
+        <v>123526</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="4">
-        <v>123526</v>
+      <c r="B56" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="3">
+        <v>123581</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="4">
-        <v>123581</v>
+      <c r="B57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="3">
+        <v>123527</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C58" s="4">
-        <v>123527</v>
+      <c r="B58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="3">
+        <v>123570</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C59" s="4">
-        <v>123570</v>
+      <c r="B59" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" s="3">
+        <v>123599</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C60" s="4">
-        <v>123599</v>
+      <c r="B60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="3">
+        <v>123550</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="4">
-        <v>123550</v>
+      <c r="B61" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="3">
+        <v>123547</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="4">
-        <v>123547</v>
+      <c r="B62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="3">
+        <v>123594</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63" s="4">
-        <v>123594</v>
+      <c r="B63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="3">
+        <v>123557</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="4">
-        <v>123557</v>
+      <c r="B64" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="3">
+        <v>123601</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65" s="4">
-        <v>123601</v>
+      <c r="B65" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3">
+        <v>123456</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" s="4">
-        <v>123456</v>
+      <c r="B66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="3">
+        <v>123532</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C67" s="4">
-        <v>123532</v>
+      <c r="B67" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C67" s="3">
+        <v>123624</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C68" s="4">
-        <v>123624</v>
+      <c r="B68" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="3">
+        <v>123485</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="4">
-        <v>123485</v>
+      <c r="B69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="3">
+        <v>123548</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" s="4">
-        <v>123548</v>
+      <c r="B70" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="3">
+        <v>123611</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C71" s="4">
-        <v>123611</v>
+      <c r="B71" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="3">
+        <v>123492</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C72" s="4">
-        <v>123492</v>
+      <c r="B72" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="3">
+        <v>123572</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" s="4">
-        <v>123572</v>
+      <c r="B73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" s="3">
+        <v>123544</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="4">
-        <v>123544</v>
+      <c r="B74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="3">
+        <v>123469</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" s="4">
-        <v>123469</v>
+      <c r="B75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="3">
+        <v>123498</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="4">
-        <v>123498</v>
+      <c r="B76" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" s="3">
+        <v>123567</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" s="4">
-        <v>123567</v>
+      <c r="B77" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" s="3">
+        <v>123564</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C78" s="4">
-        <v>123564</v>
+      <c r="B78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="3">
+        <v>123489</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="4">
-        <v>123489</v>
+      <c r="B79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="3">
+        <v>123475</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="4">
-        <v>123475</v>
+      <c r="B80" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C80" s="3">
+        <v>123610</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B81" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="4">
-        <v>123610</v>
+      <c r="B81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="3">
+        <v>123471</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B82" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="4">
-        <v>123471</v>
+      <c r="B82" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="3">
+        <v>123571</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B83" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C83" s="4">
-        <v>123571</v>
+      <c r="B83" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C83" s="3">
+        <v>123588</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B84" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C84" s="4">
-        <v>123588</v>
+      <c r="B84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3">
+        <v>123458</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B85" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C85" s="4">
-        <v>123458</v>
+      <c r="B85" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="3">
+        <v>123486</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B86" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="4">
-        <v>123486</v>
+      <c r="B86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" s="3">
+        <v>123494</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="4">
-        <v>123494</v>
+      <c r="B87" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="3">
+        <v>123561</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C88" s="4">
-        <v>123561</v>
+      <c r="B88" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C88" s="3">
+        <v>123488</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B89" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C89" s="4">
-        <v>123488</v>
+      <c r="B89" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C89" s="3">
+        <v>123560</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B90" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C90" s="4">
-        <v>123560</v>
+      <c r="B90" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C90" s="3">
+        <v>123513</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C91" s="4">
-        <v>123513</v>
+      <c r="B91" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="3">
+        <v>123479</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B92" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" s="4">
-        <v>123479</v>
+      <c r="B92" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C92" s="3">
+        <v>123619</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C93" s="4">
-        <v>123619</v>
+      <c r="B93" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" s="3">
+        <v>123585</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B94" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C94" s="4">
-        <v>123585</v>
+      <c r="B94" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94" s="3">
+        <v>123556</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B95" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C95" s="4">
-        <v>123556</v>
+      <c r="B95" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="3">
+        <v>123481</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B96" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C96" s="4">
-        <v>123481</v>
+      <c r="B96" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" s="3">
+        <v>123540</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C97" s="4">
-        <v>123540</v>
+      <c r="B97" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C97" s="3">
+        <v>123608</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C98" s="4">
-        <v>123608</v>
+      <c r="B98" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C98" s="3">
+        <v>123613</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C99" s="4">
-        <v>123613</v>
+      <c r="B99" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C99" s="3">
+        <v>123534</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C100" s="4">
-        <v>123534</v>
+      <c r="B100" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" s="3">
+        <v>123618</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B101" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C101" s="4">
-        <v>123618</v>
+      <c r="B101" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C101" s="3">
+        <v>123627</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B102" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C102" s="4">
-        <v>123627</v>
+      <c r="B102" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C102" s="3">
+        <v>123565</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B103" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C103" s="4">
-        <v>123565</v>
+      <c r="B103" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" s="3">
+        <v>123493</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B104" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="4">
-        <v>123493</v>
+      <c r="B104" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C104" s="3">
+        <v>123622</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C105" s="4">
-        <v>123622</v>
+      <c r="B105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="3">
+        <v>123467</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C106" s="4">
-        <v>123467</v>
+      <c r="B106" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106" s="3">
+        <v>123568</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C107" s="4">
-        <v>123568</v>
+      <c r="B107" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" s="3">
+        <v>123490</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C108" s="4">
-        <v>123490</v>
+      <c r="B108" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C108" s="3">
+        <v>123589</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C109" s="4">
-        <v>123589</v>
+      <c r="B109" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" s="3">
+        <v>123524</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C110" s="4">
-        <v>123524</v>
+      <c r="B110" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" s="3">
+        <v>123472</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" s="4">
-        <v>123472</v>
+      <c r="B111" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C111" s="3">
+        <v>123533</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C112" s="4">
-        <v>123533</v>
+      <c r="B112" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C112" s="3">
+        <v>123495</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C113" s="4">
-        <v>123495</v>
+      <c r="B113" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C113" s="3">
+        <v>123511</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C114" s="4">
-        <v>123511</v>
+      <c r="B114" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C114" s="3">
+        <v>123602</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C115" s="4">
-        <v>123602</v>
+      <c r="B115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" s="3">
+        <v>123465</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B116" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" s="4">
-        <v>123465</v>
+      <c r="B116" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="3">
+        <v>123487</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B117" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C117" s="4">
-        <v>123487</v>
+      <c r="B117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C117" s="3">
+        <v>123516</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B118" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C118" s="4">
-        <v>123516</v>
+      <c r="B118" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C118" s="3">
+        <v>123543</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C119" s="4">
-        <v>123543</v>
+        <v>165</v>
+      </c>
+      <c r="C119" s="3">
+        <v>123620</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B120" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C120" s="4">
-        <v>123620</v>
+      <c r="B120" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C120" s="3">
+        <v>123518</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B121" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C121" s="4">
-        <v>123518</v>
+      <c r="B121" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C121" s="3">
+        <v>123509</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B122" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C122" s="4">
-        <v>123509</v>
+      <c r="B122" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C122" s="3">
+        <v>123552</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B123" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C123" s="4">
-        <v>123552</v>
+      <c r="B123" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" s="3">
+        <v>123592</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B124" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C124" s="4">
-        <v>123592</v>
+      <c r="B124" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C124" s="3">
+        <v>123600</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B125" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C125" s="4">
-        <v>123600</v>
+      <c r="B125" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C125" s="3">
+        <v>123504</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B126" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C126" s="4">
-        <v>123504</v>
+      <c r="B126" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C126" s="3">
+        <v>123539</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C127" s="4">
-        <v>123539</v>
+        <v>124</v>
+      </c>
+      <c r="C127" s="3">
+        <v>123579</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B128" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C128" s="4">
-        <v>123579</v>
+      <c r="B128" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C128" s="3">
+        <v>123558</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C129" s="4">
-        <v>123558</v>
+      <c r="B129" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C129" s="3">
+        <v>123617</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C130" s="4">
-        <v>123617</v>
+      <c r="B130" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C130" s="3">
+        <v>123609</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C131" s="4">
-        <v>123609</v>
+      <c r="B131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" s="3">
+        <v>123466</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="4">
-        <v>123466</v>
+      <c r="B132" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C132" s="3">
+        <v>123615</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C133" s="4">
-        <v>123615</v>
+      <c r="B133" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C133" s="3">
+        <v>123603</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B134" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C134" s="4">
-        <v>123603</v>
+      <c r="B134" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C134" s="3">
+        <v>123616</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B135" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C135" s="4">
-        <v>123616</v>
+      <c r="B135" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C135" s="3">
+        <v>123576</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C136" s="4">
-        <v>123576</v>
+      <c r="B136" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C136" s="3">
+        <v>123632</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B137" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C137" s="4">
-        <v>123632</v>
+      <c r="B137" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" s="3">
+        <v>123633</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B138" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C138" s="4">
-        <v>123633</v>
+      <c r="B138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" s="3">
+        <v>123468</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B139" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C139" s="4">
-        <v>123468</v>
+      <c r="B139" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C139" s="3">
+        <v>123629</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B140" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C140" s="4">
-        <v>123629</v>
+      <c r="B140" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C140" s="3">
+        <v>123587</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B141" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C141" s="4">
-        <v>123587</v>
+      <c r="B141" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C141" s="3">
+        <v>123549</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B142" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C142" s="4">
-        <v>123549</v>
+      <c r="B142" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C142" s="3">
+        <v>123577</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B143" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C143" s="4">
-        <v>123577</v>
+      <c r="B143" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C143" s="3">
+        <v>123506</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B144" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C144" s="4">
-        <v>123506</v>
+      <c r="B144" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C144" s="3">
+        <v>123591</v>
       </c>
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B145" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C145" s="4">
-        <v>123591</v>
+      <c r="B145" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C145" s="3">
+        <v>123546</v>
       </c>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B146" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C146" s="4">
-        <v>123546</v>
+      <c r="B146" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C146" s="3">
+        <v>123598</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B147" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C147" s="4">
-        <v>123598</v>
+      <c r="B147" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C147" s="3">
+        <v>123607</v>
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B148" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C148" s="4">
-        <v>123607</v>
+      <c r="B148" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C148" s="3">
+        <v>123621</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B149" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C149" s="4">
-        <v>123621</v>
+      <c r="B149" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C149" s="3">
+        <v>123502</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B150" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C150" s="4">
-        <v>123502</v>
+      <c r="B150" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C150" s="3">
+        <v>123593</v>
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B151" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C151" s="4">
-        <v>123593</v>
+      <c r="B151" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C151" s="3">
+        <v>123522</v>
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B152" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C152" s="4">
-        <v>123522</v>
+      <c r="B152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C152" s="3">
+        <v>123499</v>
       </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B153" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C153" s="4">
-        <v>123499</v>
+      <c r="B153" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C153" s="3">
+        <v>123563</v>
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B154" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C154" s="4">
-        <v>123563</v>
+      <c r="B154" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C154" s="3">
+        <v>123569</v>
       </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B155" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C155" s="4">
-        <v>123569</v>
+      <c r="B155" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="3">
+        <v>123482</v>
       </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B156" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C156" s="4">
-        <v>123482</v>
+      <c r="B156" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C156" s="3">
+        <v>123623</v>
       </c>
     </row>
     <row r="157" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B157" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C157" s="4">
-        <v>123623</v>
+      <c r="B157" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="3">
+        <v>123480</v>
       </c>
     </row>
     <row r="158" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B158" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C158" s="4">
-        <v>123480</v>
+      <c r="B158" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C158" s="3">
+        <v>123512</v>
       </c>
     </row>
     <row r="159" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B159" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C159" s="4">
-        <v>123512</v>
+      <c r="B159" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C159" s="3">
+        <v>123595</v>
       </c>
     </row>
     <row r="160" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B160" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C160" s="4">
-        <v>123595</v>
+      <c r="B160" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="3">
+        <v>123463</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B161" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="4">
-        <v>123463</v>
+      <c r="B161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="3">
+        <v>123476</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B162" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C162" s="4">
-        <v>123476</v>
+      <c r="B162" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C162" s="3">
+        <v>123477</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B163" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C163" s="4">
-        <v>123477</v>
+      <c r="B163" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C163" s="3">
+        <v>123457</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B164" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C164" s="4">
-        <v>123457</v>
+      <c r="B164" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="3">
+        <v>123459</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B165" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C165" s="4">
-        <v>123459</v>
+      <c r="B165" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C165" s="3">
+        <v>123583</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B166" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C166" s="4">
-        <v>123583</v>
+      <c r="B166" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C166" s="3">
+        <v>123575</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B167" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C167" s="4">
-        <v>123575</v>
+      <c r="B167" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C167" s="3">
+        <v>123515</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B168" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C168" s="4">
-        <v>123515</v>
+      <c r="B168" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C168" s="3">
+        <v>123606</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B169" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C169" s="4">
-        <v>123606</v>
+      <c r="B169" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C169" s="3">
+        <v>123553</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B170" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C170" s="4">
-        <v>123553</v>
+      <c r="B170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="3">
+        <v>123478</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B171" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C171" s="4">
-        <v>123478</v>
+      <c r="B171" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C171" s="3">
+        <v>123519</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B172" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C172" s="4">
-        <v>123519</v>
+      <c r="B172" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C172" s="3">
+        <v>123528</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B173" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C173" s="4">
-        <v>123528</v>
+      <c r="B173" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C173" s="3">
+        <v>123464</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B174" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C174" s="4">
-        <v>123464</v>
+      <c r="B174" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C174" s="3">
+        <v>123559</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B175" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C175" s="4">
-        <v>123559</v>
+      <c r="B175" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C175" s="3">
+        <v>123612</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B176" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C176" s="4">
-        <v>123612</v>
+      <c r="B176" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C176" s="3">
+        <v>123605</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B177" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C177" s="4">
-        <v>123605</v>
+      <c r="B177" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C177" s="3">
+        <v>123510</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B178" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C178" s="4">
-        <v>123510</v>
-      </c>
-    </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B179" s="6" t="s">
+      <c r="B178" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C179" s="4">
+      <c r="C178" s="3">
         <v>123628</v>
       </c>
     </row>
-    <row r="180" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B180" s="9" t="s">
+    <row r="179" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B179" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C180" s="4">
+      <c r="C179" s="3">
         <v>123584</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:C180">
-    <sortCondition ref="B1:B180"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C179">
+    <sortCondition ref="B1:B179"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
